--- a/src/04_drt_simulation/경기도_DRT_재배치_시뮬레이션_v2.xlsx
+++ b/src/04_drt_simulation/경기도_DRT_재배치_시뮬레이션_v2.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -469,7 +469,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>총 운행대수: 312대 (이천시내권 미포함 — 추가 확인 중), 21개 시군 60개 운행구역</t>
+          <t>총 운행대수: 326대 (이천시내권 14대 포함, 전체 시군 확보 완료), 21개 시군 61개 운행구역</t>
         </is>
       </c>
     </row>
@@ -532,6 +532,16 @@
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>- 미확인: 근거 부족으로 귀속 안 함(고양 고봉동·식사동·향동동, 광주 태전동·고산동, 안산 스마트허브 — 총 26대)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>귀속 성공: 300대/326대(92.0%), 97개 운행구역 중 귀속된 읍면동 100개</t>
         </is>
       </c>
     </row>
@@ -967,7 +977,7 @@
         <v>0.342</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>3</v>
@@ -1003,7 +1013,7 @@
         <v>0.339</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -1037,7 +1047,7 @@
         <v>0.339</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -3922,10 +3932,12 @@
         <v>1</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v/>
+        <v>3.5</v>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4198,10 +4210,12 @@
         <v>1</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v/>
+        <v>3.5</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4370,10 +4384,12 @@
         <v>1</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v/>
+        <v>3.5</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -6778,10 +6794,12 @@
         <v>1</v>
       </c>
       <c r="F180" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" s="2" t="n">
-        <v/>
+        <v>3.5</v>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -11027,7 +11045,7 @@
         <v>0.101</v>
       </c>
       <c r="E304" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F304" s="2" t="n">
         <v>0</v>
@@ -11061,7 +11079,7 @@
         <v>0.101</v>
       </c>
       <c r="E305" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F305" s="2" t="n">
         <v>0</v>
@@ -11095,7 +11113,7 @@
         <v>0.101</v>
       </c>
       <c r="E306" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F306" s="2" t="n">
         <v>0</v>
@@ -11129,7 +11147,7 @@
         <v>0.101</v>
       </c>
       <c r="E307" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F307" s="2" t="n">
         <v>0</v>
@@ -11163,7 +11181,7 @@
         <v>0.1</v>
       </c>
       <c r="E308" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F308" s="2" t="n">
         <v>0</v>
@@ -11197,7 +11215,7 @@
         <v>0.1</v>
       </c>
       <c r="E309" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F309" s="2" t="n">
         <v>0</v>
@@ -11231,7 +11249,7 @@
         <v>0.1</v>
       </c>
       <c r="E310" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F310" s="2" t="n">
         <v>0</v>
@@ -11265,7 +11283,7 @@
         <v>0.1</v>
       </c>
       <c r="E311" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F311" s="2" t="n">
         <v>0</v>
@@ -11299,7 +11317,7 @@
         <v>0.1</v>
       </c>
       <c r="E312" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -11333,7 +11351,7 @@
         <v>0.099</v>
       </c>
       <c r="E313" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F313" s="2" t="n">
         <v>0</v>
@@ -11367,7 +11385,7 @@
         <v>0.099</v>
       </c>
       <c r="E314" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F314" s="2" t="n">
         <v>0</v>
@@ -22663,7 +22681,7 @@
         <v>0.339</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -22697,7 +22715,7 @@
         <v>0.339</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>

--- a/src/04_drt_simulation/경기도_DRT_재배치_시뮬레이션_v2.xlsx
+++ b/src/04_drt_simulation/경기도_DRT_재배치_시뮬레이션_v2.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체602_재배치결과'!$A$1:$H$603</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'과잉배치_의심지역'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'과잉배치_의심지역'!$A$1:$H$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'신규후보_상위30'!$A$1:$H$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,7 +531,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>- 미확인: 근거 부족으로 귀속 안 함(고양 고봉동·식사동·향동동, 광주 태전동·고산동, 안산 스마트허브 — 총 26대)</t>
+          <t>- 미확인: 근거 부족으로 귀속 안 함(고양 향동동, 광주 태전동·고산동, 안산 스마트허브 — 총 19대)</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>귀속 성공: 300대/326대(92.0%), 97개 운행구역 중 귀속된 읍면동 100개</t>
+          <t>귀속 성공: 307대/326대(94.2%), 61개 운행구역 중 귀속된 읍면동 103개</t>
         </is>
       </c>
     </row>
@@ -5418,10 +5418,12 @@
         <v>1</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -16312,10 +16314,12 @@
         <v>0</v>
       </c>
       <c r="F458" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G458" s="2" t="n">
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
@@ -21293,7 +21297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -21860,12 +21864,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>수원시권선구</t>
+          <t>고양시일산동구</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>평동</t>
+          <t>식사동</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -21875,16 +21879,16 @@
         <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>후보</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>읍면동 미확인(해당 시군 운행 기록 있음)</t>
+          <t>운행구역에 읍면동 명시</t>
         </is>
       </c>
     </row>
@@ -21896,31 +21900,31 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>부천시오정구</t>
+          <t>수원시권선구</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>고강본동</t>
+          <t>평동</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.079</v>
+        <v>0.076</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>후보</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>운행구역에 읍면동 명시</t>
+          <t>읍면동 미확인(해당 시군 운행 기록 있음)</t>
         </is>
       </c>
     </row>
@@ -21932,22 +21936,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>부천시소사구</t>
+          <t>부천시오정구</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>옥길동</t>
+          <t>고강본동</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -21968,22 +21972,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>부천시소사구</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>고촌읍</t>
+          <t>옥길동</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -22004,12 +22008,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>시흥시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>신천동</t>
+          <t>고촌읍</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -22019,7 +22023,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -22028,7 +22032,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>제공 CSV에 해당 시군 기록 없음</t>
+          <t>운행구역에 읍면동 명시</t>
         </is>
       </c>
     </row>
@@ -22040,22 +22044,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>부천시소사구</t>
+          <t>시흥시</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>범박동</t>
+          <t>신천동</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -22064,7 +22068,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>운행구역에 읍면동 명시</t>
+          <t>제공 CSV에 해당 시군 기록 없음</t>
         </is>
       </c>
     </row>
@@ -22076,22 +22080,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>수원시영통구</t>
+          <t>부천시소사구</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>광교1동</t>
+          <t>범박동</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -22112,12 +22116,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>수원시영통구</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>풍무동</t>
+          <t>광교1동</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -22127,7 +22131,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -22148,12 +22152,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>수원시권선구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>입북동</t>
+          <t>풍무동</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -22163,16 +22167,16 @@
         <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>후보</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>읍면동 미확인(해당 시군 운행 기록 있음)</t>
+          <t>운행구역에 읍면동 명시</t>
         </is>
       </c>
     </row>
@@ -22184,22 +22188,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>의정부시</t>
+          <t>수원시권선구</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>송산2동</t>
+          <t>입북동</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -22220,12 +22224,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>화성시동탄구</t>
+          <t>의정부시</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>동탄8동</t>
+          <t>송산2동</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -22235,7 +22239,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>2.222</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -22256,31 +22260,31 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>수원시영통구</t>
+          <t>화성시동탄구</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>광교2동</t>
+          <t>동탄8동</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.089</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>6</v>
+        <v>2.222</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>후보</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>운행구역에 읍면동 명시</t>
+          <t>읍면동 미확인(해당 시군 운행 기록 있음)</t>
         </is>
       </c>
     </row>
@@ -22292,22 +22296,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>광명시</t>
+          <t>수원시영통구</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>일직동</t>
+          <t>광교2동</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.09</v>
+        <v>0.089</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -22316,7 +22320,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>제공 CSV에 해당 시군 기록 없음</t>
+          <t>운행구역에 읍면동 명시</t>
         </is>
       </c>
     </row>
@@ -22328,36 +22332,72 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
+          <t>광명시</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>일직동</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>제공 CSV에 해당 시군 기록 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>파주시</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>운정4동</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D30" s="2" t="n">
         <v>0.094</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="n">
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>확인</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>운행구역에 읍면동 명시</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H29"/>
+  <autoFilter ref="A1:H30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
